--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484625_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484625_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5404</v>
+        <v>2.4471</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7095</v>
+        <v>0.5172</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8308</v>
+        <v>1.9299</v>
       </c>
       <c r="G2" t="n">
         <v>2.0897</v>
@@ -610,13 +610,13 @@
         <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.09909999999999999</v>
+        <v>-0.1923</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1297</v>
+        <v>-0.322</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0306</v>
+        <v>0.1297</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.245</v>
+        <v>2.3358</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2601</v>
+        <v>1.4253</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9849</v>
+        <v>0.9106</v>
       </c>
       <c r="G3" t="n">
         <v>0.1216</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1778</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0166</v>
+        <v>0.1818</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1944</v>
+        <v>-0.2687</v>
       </c>
       <c r="V3" t="n">
         <v>1.5681</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5274</v>
+        <v>1.3436</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4421</v>
+        <v>0.2087</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0853</v>
+        <v>1.1349</v>
       </c>
       <c r="G4" t="n">
         <v>0.4583</v>
@@ -766,13 +766,13 @@
         <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9305</v>
+        <v>0.7466</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7308</v>
+        <v>0.4974</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1997</v>
+        <v>0.2492</v>
       </c>
       <c r="V4" t="n">
         <v>0.3219</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9106</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1914</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7192</v>
+        <v>0.744</v>
       </c>
       <c r="G5" t="n">
         <v>0.08019999999999999</v>
@@ -844,13 +844,13 @@
         <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1078</v>
+        <v>0.0092</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1999</v>
+        <v>0.0766</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0921</v>
+        <v>-0.0673</v>
       </c>
       <c r="V5" t="n">
         <v>-0.0104</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. ROIG ARIÑO</t>
+          <t>G. BORREGA BERTOLIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6502</v>
+        <v>0.7426</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6502</v>
+        <v>-1.3469</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2.0894</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6502</v>
+        <v>-1.6451</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6502</v>
+        <v>-0.0074</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-1.6377</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6502</v>
+        <v>-1.0814</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6502</v>
+        <v>-0.5018</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.5797</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.5636</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.4944</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-1.0581</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.6465</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.6161</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.0304</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.5681</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. CORTINA CAMPOS</t>
+          <t>T. ROIG ARIÑO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4001</v>
+        <v>0.6502</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1547</v>
+        <v>0.6502</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2455</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3125</v>
+        <v>0.6502</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7388</v>
+        <v>0.6502</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4263</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6509</v>
+        <v>0.6502</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.641</v>
+        <v>0.6502</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2919</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9633</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0977</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8656</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7126</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4201</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2925</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. BORREGA BERTOLIN</t>
+          <t>X. CORTINA CAMPOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0418</v>
+        <v>0.15</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9238</v>
+        <v>0.1275</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9656</v>
+        <v>0.0225</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6451</v>
+        <v>-0.3125</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0074</v>
+        <v>-0.7388</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6377</v>
+        <v>0.4263</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0814</v>
+        <v>0.6509</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5018</v>
+        <v>-0.641</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5797</v>
+        <v>1.2919</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5636</v>
+        <v>-0.9633</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4944</v>
+        <v>-0.0977</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0581</v>
+        <v>-0.8656</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3823</v>
+        <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3473</v>
+        <v>0.4625</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.193</v>
+        <v>0.3929</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1542</v>
+        <v>0.0696</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5681</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4255</v>
+        <v>-0.0598</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8941</v>
+        <v>-0.7018</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4685</v>
+        <v>0.642</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2553</v>
@@ -1156,13 +1156,13 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6363</v>
+        <v>-0.2705</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3673</v>
+        <v>-0.175</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.269</v>
+        <v>-0.0956</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6335</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>J. SAEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2396</v>
+        <v>-1.021</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9733</v>
+        <v>-1.8607</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7337</v>
+        <v>0.8398</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.785</v>
+        <v>-2.2806</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9929</v>
+        <v>-0.9537</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7921</v>
+        <v>-1.3269</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6276</v>
+        <v>-1.7415</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6692</v>
+        <v>-1.152</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0417</v>
+        <v>-0.5895</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1575</v>
+        <v>-0.5391</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3237</v>
+        <v>0.1983</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8338</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8911</v>
+        <v>-0.3897</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1441</v>
+        <v>-0.4412</v>
       </c>
       <c r="U10" t="n">
-        <v>0.747</v>
+        <v>0.0515</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3428</v>
+        <v>0.3219</v>
       </c>
       <c r="X10" t="n">
         <v>-0.3219</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SAEZ GONZALEZ</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4359</v>
+        <v>-1.7182</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3004</v>
+        <v>-2.0555</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8645</v>
+        <v>0.3373</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2806</v>
+        <v>-1.785</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9537</v>
+        <v>-0.9929</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3269</v>
+        <v>-0.7921</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7415</v>
+        <v>-0.6276</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.152</v>
+        <v>-0.6692</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5895</v>
+        <v>0.0417</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5391</v>
+        <v>-1.1575</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1983</v>
+        <v>-0.3237</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.8338</v>
       </c>
       <c r="P11" t="n">
-        <v>1.6493</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8046</v>
+        <v>0.4125</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8808</v>
+        <v>0.0619</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0762</v>
+        <v>0.3506</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3219</v>
+        <v>0.3428</v>
       </c>
       <c r="X11" t="n">
         <v>-0.3219</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. FERRI BARCENAS</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1651</v>
+        <v>-2.5203</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9364</v>
+        <v>-1.4153</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7713</v>
+        <v>-1.105</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.9664</v>
+        <v>-0.0458</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9948</v>
+        <v>0.9735</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.9717</v>
+        <v>-1.0193</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.7372</v>
+        <v>-0.0759</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.016</v>
+        <v>0.4302</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.7211</v>
+        <v>-0.5062</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2293</v>
+        <v>0.0302</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0213</v>
+        <v>0.5433</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2505</v>
+        <v>-0.5131</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0005</v>
+        <v>-0.8569</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6388</v>
+        <v>-0.4231</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3617</v>
+        <v>-0.4338</v>
       </c>
       <c r="V12" t="n">
-        <v>2.5339</v>
+        <v>-2.5339</v>
       </c>
       <c r="W12" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6231</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2566</v>
+        <v>-3.3195</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3453</v>
+        <v>-3.4826</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0887</v>
+        <v>0.1631</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4049</v>
@@ -1468,13 +1468,13 @@
         <v>1.4661</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1345</v>
+        <v>-0.1974</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0015</v>
+        <v>-0.1387</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.133</v>
+        <v>-0.0586</v>
       </c>
       <c r="V13" t="n">
         <v>-1.267</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>P. FERRI BARCENAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.3922</v>
+        <v>-3.3409</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.9651</v>
+        <v>-4.9635</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4271</v>
+        <v>1.6227</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0458</v>
+        <v>-5.9664</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9735</v>
+        <v>-0.9948</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0193</v>
+        <v>-4.9717</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0759</v>
+        <v>-4.7372</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4302</v>
+        <v>-1.016</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5062</v>
+        <v>-3.7211</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0302</v>
+        <v>-1.2293</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5433</v>
+        <v>0.0213</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5131</v>
+        <v>-1.2505</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9163</v>
+        <v>-0.733</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8326</v>
+        <v>2.0158</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.7287</v>
+        <v>0.8247</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9728</v>
+        <v>0.6116</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7559</v>
+        <v>0.213</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.5339</v>
+        <v>2.5339</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.5339</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.599400000000001</v>
+        <v>-3.498400000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.9304</v>
+        <v>-12.8293</v>
       </c>
       <c r="F15" t="n">
-        <v>9.3309</v>
+        <v>9.331200000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-11.2956</v>
@@ -1606,13 +1606,13 @@
         <v>-4.1646</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.834800000000001</v>
+        <v>-5.8348</v>
       </c>
       <c r="N15" t="n">
         <v>3.4638</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.298599999999999</v>
+        <v>-9.2986</v>
       </c>
       <c r="P15" t="n">
         <v>6.414</v>
@@ -1624,16 +1624,16 @@
         <v>19.242</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2858</v>
+        <v>-0.1846999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3948</v>
+        <v>-0.2938999999999997</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1091</v>
+        <v>0.1092</v>
       </c>
       <c r="V15" t="n">
-        <v>1.568000000000001</v>
+        <v>1.568</v>
       </c>
       <c r="W15" t="n">
         <v>5.7534</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2184</v>
+        <v>5.9658</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8164</v>
+        <v>1.1048</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4021</v>
+        <v>4.861</v>
       </c>
       <c r="G16" t="n">
         <v>3.9015</v>
@@ -1702,13 +1702,13 @@
         <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0133</v>
+        <v>0.7607</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3506</v>
+        <v>-0.0622</v>
       </c>
       <c r="U16" t="n">
-        <v>0.364</v>
+        <v>0.8229</v>
       </c>
       <c r="V16" t="n">
         <v>0.0208</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0031</v>
+        <v>3.2711</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1942</v>
+        <v>-0.2903</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1973</v>
+        <v>3.5615</v>
       </c>
       <c r="G17" t="n">
         <v>6.5282</v>
@@ -1780,13 +1780,13 @@
         <v>2.3823</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5615</v>
+        <v>0.8296</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0332</v>
+        <v>-0.0629</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5283</v>
+        <v>0.8925</v>
       </c>
       <c r="V17" t="n">
         <v>0.3115</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0777</v>
+        <v>2.8498</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2063</v>
+        <v>1.4948</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8713</v>
+        <v>1.355</v>
       </c>
       <c r="G18" t="n">
         <v>1.7364</v>
@@ -1858,13 +1858,13 @@
         <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3917</v>
+        <v>0.3805</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2021</v>
+        <v>0.0864</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1896</v>
+        <v>0.2941</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2667</v>
+        <v>1.3163</v>
       </c>
       <c r="E19" t="n">
         <v>0.1126</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1541</v>
+        <v>1.2037</v>
       </c>
       <c r="G19" t="n">
         <v>0.8853</v>
@@ -1936,13 +1936,13 @@
         <v>0.5498</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0149</v>
+        <v>0.0645</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1801</v>
+        <v>0.2296</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. KABASELE KATUMBA</t>
+          <t>J. BALFAGON MIRAVET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.299</v>
+        <v>0.3351</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7417</v>
+        <v>-3.1067</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4427</v>
+        <v>3.4418</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3267</v>
+        <v>1.6686</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-0.1844</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4263</v>
+        <v>1.8531</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.311</v>
+        <v>-0.3472</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0959</v>
+        <v>-1.1428</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4069</v>
+        <v>0.7956</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6377</v>
+        <v>2.0158</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1955</v>
+        <v>0.9584</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8332000000000001</v>
+        <v>1.0575</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0995</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9321</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4617</v>
+        <v>0.3158</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7308</v>
+        <v>-0.1493</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2691</v>
+        <v>0.4651</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0.3219</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.9109</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. BALFAGON SULLER</t>
+          <t>B. KABASELE KATUMBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3278</v>
+        <v>0.2495</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1125</v>
+        <v>0.3571</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7847</v>
+        <v>-0.1076</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1072</v>
+        <v>0.3267</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2384</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8688</v>
+        <v>0.4263</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7452</v>
+        <v>-0.311</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2292</v>
+        <v>0.0959</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.516</v>
+        <v>-0.4069</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.362</v>
+        <v>0.6377</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0092</v>
+        <v>-0.1955</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3528</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1369</v>
+        <v>0.4121</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3673</v>
+        <v>0.3462</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2304</v>
+        <v>0.066</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. CALANCHE GONZALEZ</t>
+          <t>M. BALFAGON SULLER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9032</v>
+        <v>-0.2273</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0585</v>
+        <v>-1.0163</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8447</v>
+        <v>0.789</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8245</v>
+        <v>-1.1072</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6737</v>
+        <v>-0.2384</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1508</v>
+        <v>-0.8688</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1067</v>
+        <v>-0.7452</v>
       </c>
       <c r="K22" t="n">
-        <v>0.065</v>
+        <v>-0.2292</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0417</v>
+        <v>-0.516</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9312</v>
+        <v>-0.362</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7388</v>
+        <v>-0.0092</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1925</v>
+        <v>-0.3528</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6284</v>
+        <v>-0.0364</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1652</v>
+        <v>-0.2711</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4633</v>
+        <v>0.2347</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>M. CALANCHE GONZALEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0745</v>
+        <v>-0.6045</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0671</v>
+        <v>0.0377</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9926</v>
+        <v>-0.6422</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2969</v>
+        <v>-0.8245</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8224</v>
+        <v>-0.6737</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5254</v>
+        <v>-0.1508</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7405</v>
+        <v>0.1067</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.6574</v>
+        <v>0.065</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.0417</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4436</v>
+        <v>-0.9312</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.165</v>
+        <v>-0.7388</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6086</v>
+        <v>-0.1925</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.8484</v>
+        <v>0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.8642</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1154</v>
+        <v>-0.3298</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9933</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1221</v>
+        <v>-0.2608</v>
       </c>
       <c r="V23" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.5444</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BALFAGON MIRAVET</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.339</v>
+        <v>-2.9802</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8759</v>
+        <v>-4.6056</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5369</v>
+        <v>1.6254</v>
       </c>
       <c r="G24" t="n">
-        <v>1.6686</v>
+        <v>-1.2969</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1844</v>
+        <v>-2.8224</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8531</v>
+        <v>1.5254</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3472</v>
+        <v>-1.7405</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1428</v>
+        <v>-2.6574</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7956</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="M24" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.165</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.6086</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-3.8484</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-5.8642</v>
+      </c>
+      <c r="R24" t="n">
         <v>2.0158</v>
       </c>
-      <c r="N24" t="n">
-        <v>0.9584</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.0575</v>
-      </c>
-      <c r="P24" t="n">
-        <v>-1.6493</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-2.9321</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.2828</v>
-      </c>
       <c r="S24" t="n">
-        <v>-1.3583</v>
+        <v>1.2096</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9185</v>
+        <v>0.4548</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4398</v>
+        <v>0.7549</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3219</v>
+        <v>2.5444</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6212</v>
+        <v>-3.0122</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8999</v>
+        <v>-3.4191</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2787</v>
+        <v>0.4069</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5224</v>
@@ -2404,13 +2404,13 @@
         <v>1.6493</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3658</v>
+        <v>0.2432</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6976</v>
+        <v>-0.2168</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3318</v>
+        <v>0.46</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.5992</v>
+        <v>7.163400000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.331100000000001</v>
+        <v>-9.331</v>
       </c>
       <c r="F26" t="n">
-        <v>13.9303</v>
+        <v>16.4945</v>
       </c>
       <c r="G26" t="n">
         <v>11.2957</v>
@@ -2482,13 +2482,13 @@
         <v>12.8279</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2857</v>
+        <v>3.8498</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1091999999999999</v>
+        <v>-0.1091</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3949</v>
+        <v>3.959</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5682</v>
@@ -2497,7 +2497,7 @@
         <v>4.1853</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.753400000000001</v>
+        <v>-5.753399999999999</v>
       </c>
     </row>
   </sheetData>
